--- a/data/trans_dic/P1412-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1412-Clase-trans_dic.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -683,17 +683,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,72</t>
+          <t>0,22; 2,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,6</t>
+          <t>0,59; 2,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -703,22 +703,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,44</t>
+          <t>0,27; 1,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,62</t>
+          <t>0,12; 1,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,76</t>
+          <t>0,59; 1,66</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,56</t>
+          <t>0,12; 1,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,92</t>
+          <t>0,07; 0,94</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,18</t>
+          <t>0,31; 2,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,51</t>
+          <t>0,16; 1,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,88</t>
+          <t>0,64; 2,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,66</t>
+          <t>0,22; 1,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,45</t>
+          <t>0,56; 1,99</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -1008,22 +1008,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,74</t>
+          <t>0,6; 1,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,78</t>
+          <t>0,58; 1,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,89</t>
+          <t>0,6; 1,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,73</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,9</t>
+          <t>0,28; 1,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,17</t>
+          <t>0,34; 1,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,18</t>
+          <t>0,4; 1,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,25</t>
+          <t>0,55; 1,29</t>
         </is>
       </c>
     </row>
@@ -1075,22 +1075,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,3</t>
+          <t>0,23; 1,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,17</t>
+          <t>0,57; 2,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,61</t>
+          <t>0,26; 1,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,5</t>
+          <t>0,72; 2,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,72</t>
+          <t>0,29; 1,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,86</t>
+          <t>0,31; 1,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,91</t>
+          <t>0,63; 1,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,57</t>
+          <t>0,53; 1,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,98</t>
+          <t>0,37; 0,97</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -1243,32 +1243,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,75</t>
+          <t>0,48; 1,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,85</t>
+          <t>0,51; 1,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,2</t>
+          <t>0,33; 1,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,43</t>
+          <t>0,39; 1,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,44</t>
+          <t>0,39; 1,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,89</t>
+          <t>0,26; 0,97</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,02</t>
+          <t>0,42; 1,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,13</t>
+          <t>0,52; 1,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,22</t>
+          <t>0,66; 1,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,02</t>
+          <t>0,44; 1,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,88</t>
+          <t>0,32; 0,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,69</t>
+          <t>0,4; 0,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,92</t>
+          <t>0,49; 0,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,88</t>
+          <t>0,48; 0,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,85</t>
+          <t>0,59; 0,93</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>7123</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9606</t>
+          <t>10530</t>
         </is>
       </c>
     </row>
@@ -1644,17 +1644,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>928; 11651</t>
+          <t>927; 10685</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3298; 13128</t>
+          <t>3239; 13416</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 8189</t>
+          <t>0; 7435</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1664,22 +1664,22 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1118; 6423</t>
+          <t>1297; 7288</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6386</t>
+          <t>0; 8303</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>930; 12558</t>
+          <t>921; 11034</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5088; 16771</t>
+          <t>6079; 17213</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>562</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>3150</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5784</t>
+          <t>0; 5881</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>556; 7060</t>
+          <t>587; 7392</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2666</t>
+          <t>0; 2813</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5197</t>
+          <t>0; 5210</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>828; 7652</t>
+          <t>593; 8531</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>554</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>7017</t>
         </is>
       </c>
     </row>
@@ -1965,17 +1965,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1888; 13720</t>
+          <t>1981; 15312</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>862; 7889</t>
+          <t>856; 8716</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1240; 12573</t>
+          <t>3031; 11910</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1990,22 +1990,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3067</t>
+          <t>0; 2855</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1100; 14767</t>
+          <t>1954; 14547</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>863; 7998</t>
+          <t>863; 7979</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1691; 12079</t>
+          <t>3696; 13098</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11239</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15531</t>
+          <t>17132</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6106; 20220</t>
+          <t>6949; 22183</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6539; 20502</t>
+          <t>6612; 20322</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6468; 19481</t>
+          <t>6797; 20329</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5552</t>
+          <t>0; 5031</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7613</t>
+          <t>0; 7625</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1580; 8844</t>
+          <t>2384; 9891</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7635; 22547</t>
+          <t>6551; 22073</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7942; 23318</t>
+          <t>7910; 23012</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9172; 25072</t>
+          <t>10918; 25587</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7599</t>
+          <t>8737</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1155; 11736</t>
+          <t>1155; 9953</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3154; 13480</t>
+          <t>3552; 14820</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1394; 7632</t>
+          <t>1443; 8253</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5516; 19033</t>
+          <t>5499; 18814</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2123; 12730</t>
+          <t>2135; 12777</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1994; 7226</t>
+          <t>2535; 8901</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8587; 24239</t>
+          <t>8022; 24575</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7069; 21347</t>
+          <t>7222; 21854</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4202; 12799</t>
+          <t>5115; 13594</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>5589</t>
         </is>
       </c>
     </row>
@@ -2469,32 +2469,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5345; 19425</t>
+          <t>5269; 18978</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5526; 19990</t>
+          <t>5505; 19527</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2253; 9128</t>
+          <t>2743; 10684</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5362; 19639</t>
+          <t>5335; 19404</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5530; 19651</t>
+          <t>5400; 18826</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2249; 8884</t>
+          <t>2820; 10441</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29440</t>
+          <t>31874</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17285</t>
+          <t>20281</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>46726</t>
+          <t>52155</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>14954; 35033</t>
+          <t>14513; 35481</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>16936; 38355</t>
+          <t>17441; 37390</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21211; 41283</t>
+          <t>22594; 42718</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16596; 36019</t>
+          <t>15745; 37905</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11335; 31032</t>
+          <t>11357; 30590</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11772; 24812</t>
+          <t>14621; 28233</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35826; 64291</t>
+          <t>34163; 62861</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>33239; 60714</t>
+          <t>32977; 59191</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>35465; 59257</t>
+          <t>41471; 65960</t>
         </is>
       </c>
     </row>
